--- a/data/trans_orig/P1403-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1403-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipertensión en 2007</t>
+          <t>Población con diagnóstico de hipertensión en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26167</t>
+          <t>26657</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48368</t>
+          <t>47678</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27444</t>
+          <t>27978</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50713</t>
+          <t>50828</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59135</t>
+          <t>60296</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91284</t>
+          <t>90735</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>224642</t>
+          <t>225332</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246843</t>
+          <t>246353</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>210125</t>
+          <t>210010</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>233394</t>
+          <t>232860</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>442564</t>
+          <t>443113</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>474713</t>
+          <t>473552</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,71%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35177</t>
+          <t>35799</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63016</t>
+          <t>62553</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72809</t>
+          <t>72432</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105107</t>
+          <t>106454</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>114649</t>
+          <t>113979</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156954</t>
+          <t>159875</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>430059</t>
+          <t>430522</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>457898</t>
+          <t>457276</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>398842</t>
+          <t>397495</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>431140</t>
+          <t>431517</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>840070</t>
+          <t>837149</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>882375</t>
+          <t>883045</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,57%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35317</t>
+          <t>35430</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58497</t>
+          <t>59389</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56522</t>
+          <t>56561</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86584</t>
+          <t>85896</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98002</t>
+          <t>99487</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>136484</t>
+          <t>136479</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>260349</t>
+          <t>259457</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>283529</t>
+          <t>283416</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>248828</t>
+          <t>249516</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>278890</t>
+          <t>278851</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>517774</t>
+          <t>517779</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>556256</t>
+          <t>554771</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,79%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39925</t>
+          <t>40413</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65126</t>
+          <t>65581</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54262</t>
+          <t>54668</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84235</t>
+          <t>84314</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103712</t>
+          <t>102247</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>140752</t>
+          <t>138637</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>293545</t>
+          <t>293090</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>318746</t>
+          <t>318258</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>287221</t>
+          <t>287142</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>317194</t>
+          <t>316788</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>589375</t>
+          <t>591490</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>626415</t>
+          <t>627880</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>86,0%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9627</t>
+          <t>9829</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24241</t>
+          <t>24967</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21643</t>
+          <t>20703</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42898</t>
+          <t>42247</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35424</t>
+          <t>34851</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61170</t>
+          <t>59651</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>179067</t>
+          <t>178341</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>193681</t>
+          <t>193479</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>164770</t>
+          <t>165421</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>186025</t>
+          <t>186965</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>349806</t>
+          <t>351325</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>375552</t>
+          <t>376125</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30175</t>
+          <t>30708</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54107</t>
+          <t>52935</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41311</t>
+          <t>40443</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67808</t>
+          <t>65777</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77533</t>
+          <t>76928</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>112168</t>
+          <t>111107</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>216704</t>
+          <t>217876</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240636</t>
+          <t>240103</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>210336</t>
+          <t>212367</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>236833</t>
+          <t>237701</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>436787</t>
+          <t>437848</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>471422</t>
+          <t>472027</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,99%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>71506</t>
+          <t>73028</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>106898</t>
+          <t>108448</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>93302</t>
+          <t>92119</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>129390</t>
+          <t>131120</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>173833</t>
+          <t>172214</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>223965</t>
+          <t>222523</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>508129</t>
+          <t>506579</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>543521</t>
+          <t>541999</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>508829</t>
+          <t>507099</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>544917</t>
+          <t>546100</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1029281</t>
+          <t>1030723</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1079413</t>
+          <t>1081032</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,26%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>84293</t>
+          <t>84341</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>120980</t>
+          <t>119043</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>92180</t>
+          <t>90553</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>133612</t>
+          <t>131702</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>185614</t>
+          <t>184604</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>241866</t>
+          <t>241278</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>622815</t>
+          <t>624752</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>659502</t>
+          <t>659454</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>649899</t>
+          <t>651809</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>691331</t>
+          <t>692958</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1285440</t>
+          <t>1286028</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1341692</t>
+          <t>1342702</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,91%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>388336</t>
+          <t>391893</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>465680</t>
+          <t>469366</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>528587</t>
+          <t>533039</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>619019</t>
+          <t>616523</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>945675</t>
+          <t>948521</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1060345</t>
+          <t>1059189</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2810863</t>
+          <t>2807177</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2888207</t>
+          <t>2884650</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2760178</t>
+          <t>2762674</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2850610</t>
+          <t>2846158</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5595396</t>
+          <t>5596552</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5710066</t>
+          <t>5707220</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,75%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipertensión en 2012</t>
+          <t>Población con diagnóstico de hipertensión en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22204</t>
+          <t>22588</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44779</t>
+          <t>44811</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32286</t>
+          <t>31507</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58256</t>
+          <t>55814</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60499</t>
+          <t>61148</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95292</t>
+          <t>93285</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249959</t>
+          <t>249927</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272534</t>
+          <t>272150</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>228989</t>
+          <t>231431</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>254959</t>
+          <t>255738</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>486691</t>
+          <t>488698</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>521484</t>
+          <t>520835</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,49%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64135</t>
+          <t>66338</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>100194</t>
+          <t>101065</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86019</t>
+          <t>87378</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>123923</t>
+          <t>126648</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>161747</t>
+          <t>161738</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>214215</t>
+          <t>214089</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>405333</t>
+          <t>404462</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>441392</t>
+          <t>439189</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>398733</t>
+          <t>396008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>436637</t>
+          <t>435278</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>813969</t>
+          <t>814095</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>866437</t>
+          <t>866446</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46683</t>
+          <t>46355</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76078</t>
+          <t>75307</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63020</t>
+          <t>64247</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94511</t>
+          <t>94171</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116505</t>
+          <t>117988</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159328</t>
+          <t>160694</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>247968</t>
+          <t>248739</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>277363</t>
+          <t>277691</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>246509</t>
+          <t>246849</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>278000</t>
+          <t>276773</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>505738</t>
+          <t>504372</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>548561</t>
+          <t>547078</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,26%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54359</t>
+          <t>53210</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84416</t>
+          <t>85340</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82996</t>
+          <t>83148</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118556</t>
+          <t>117101</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>145810</t>
+          <t>144938</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>191093</t>
+          <t>192394</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>289566</t>
+          <t>288642</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>319623</t>
+          <t>320772</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>270395</t>
+          <t>271850</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>305955</t>
+          <t>305803</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>571840</t>
+          <t>570539</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>617123</t>
+          <t>617995</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,0%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22549</t>
+          <t>21433</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43664</t>
+          <t>44586</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44602</t>
+          <t>45442</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71936</t>
+          <t>72038</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>73161</t>
+          <t>72376</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107430</t>
+          <t>109353</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,3%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168954</t>
+          <t>168032</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>190069</t>
+          <t>191185</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>147655</t>
+          <t>147553</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>174989</t>
+          <t>174149</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>324779</t>
+          <t>322856</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359048</t>
+          <t>359833</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,25%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51477</t>
+          <t>48626</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79077</t>
+          <t>78566</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50706</t>
+          <t>51064</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78064</t>
+          <t>79649</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>108204</t>
+          <t>108414</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>147210</t>
+          <t>146964</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>194904</t>
+          <t>195415</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>222504</t>
+          <t>225355</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>200032</t>
+          <t>198447</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>227390</t>
+          <t>227032</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>404867</t>
+          <t>405113</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>443873</t>
+          <t>443663</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,36%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>105225</t>
+          <t>105846</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>145643</t>
+          <t>148665</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>136182</t>
+          <t>139548</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>183265</t>
+          <t>182955</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>252914</t>
+          <t>256998</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>314015</t>
+          <t>317502</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>517145</t>
+          <t>514123</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>557563</t>
+          <t>556942</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>510588</t>
+          <t>510898</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>557671</t>
+          <t>554305</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1042626</t>
+          <t>1039139</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1103727</t>
+          <t>1099643</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,06%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>94470</t>
+          <t>95264</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>134741</t>
+          <t>136923</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>119075</t>
+          <t>115080</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>161012</t>
+          <t>163411</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>223681</t>
+          <t>221537</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>283740</t>
+          <t>285411</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>644357</t>
+          <t>642175</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>684628</t>
+          <t>683834</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>661566</t>
+          <t>659167</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>703503</t>
+          <t>707498</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1317936</t>
+          <t>1316265</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1377995</t>
+          <t>1380139</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,17%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>529684</t>
+          <t>529427</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>631117</t>
+          <t>618780</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>695616</t>
+          <t>691577</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>796065</t>
+          <t>792112</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1249465</t>
+          <t>1257558</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1387466</t>
+          <t>1382834</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2795662</t>
+          <t>2807999</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2897095</t>
+          <t>2897352</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2757925</t>
+          <t>2761878</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2858374</t>
+          <t>2862413</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5593303</t>
+          <t>5597935</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5731304</t>
+          <t>5723211</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,99%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipertensión en 2016</t>
+          <t>Población con diagnóstico de hipertensión en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23699</t>
+          <t>24266</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47520</t>
+          <t>47098</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24274</t>
+          <t>24114</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47066</t>
+          <t>46288</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55273</t>
+          <t>53182</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86462</t>
+          <t>88001</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>246241</t>
+          <t>246663</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270062</t>
+          <t>269495</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>241637</t>
+          <t>242415</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>264429</t>
+          <t>264589</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>496002</t>
+          <t>494463</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>527191</t>
+          <t>529282</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,87%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67065</t>
+          <t>67559</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101723</t>
+          <t>102282</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>99921</t>
+          <t>98818</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>140765</t>
+          <t>139020</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>174875</t>
+          <t>177100</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>228293</t>
+          <t>228991</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>400852</t>
+          <t>400293</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>435510</t>
+          <t>435016</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>382319</t>
+          <t>384064</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>423163</t>
+          <t>424266</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>797366</t>
+          <t>796668</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>850784</t>
+          <t>848559</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,73%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37257</t>
+          <t>35267</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62549</t>
+          <t>59208</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37005</t>
+          <t>38626</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65973</t>
+          <t>66118</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81548</t>
+          <t>80708</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118020</t>
+          <t>117275</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>256016</t>
+          <t>259357</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>281308</t>
+          <t>283298</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>270336</t>
+          <t>270191</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>299304</t>
+          <t>297683</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>536854</t>
+          <t>537599</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>573326</t>
+          <t>574166</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,68%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49186</t>
+          <t>49359</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77034</t>
+          <t>78415</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61327</t>
+          <t>61727</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93557</t>
+          <t>95616</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>118689</t>
+          <t>117765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165649</t>
+          <t>162342</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>292930</t>
+          <t>291549</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>320778</t>
+          <t>320605</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>293726</t>
+          <t>291667</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>325956</t>
+          <t>325556</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>591598</t>
+          <t>594905</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>638558</t>
+          <t>639482</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,45%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17608</t>
+          <t>18308</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37340</t>
+          <t>37807</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32976</t>
+          <t>33153</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56655</t>
+          <t>55347</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54377</t>
+          <t>57170</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85957</t>
+          <t>87000</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>173881</t>
+          <t>173414</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>193613</t>
+          <t>192913</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>161932</t>
+          <t>163240</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>185611</t>
+          <t>185434</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>343851</t>
+          <t>342808</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>375431</t>
+          <t>372638</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>86,7%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25881</t>
+          <t>26349</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48319</t>
+          <t>47605</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35563</t>
+          <t>36720</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61641</t>
+          <t>62384</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67891</t>
+          <t>66880</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100813</t>
+          <t>99741</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>214804</t>
+          <t>215518</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237242</t>
+          <t>236774</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>211474</t>
+          <t>210731</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>237552</t>
+          <t>236395</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>435425</t>
+          <t>436497</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>468347</t>
+          <t>469358</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,53%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>77410</t>
+          <t>76334</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>114576</t>
+          <t>113429</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>81196</t>
+          <t>80143</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>118435</t>
+          <t>119836</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>168674</t>
+          <t>167801</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>223541</t>
+          <t>221399</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>541982</t>
+          <t>543129</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>579148</t>
+          <t>580224</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>572859</t>
+          <t>571458</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>610098</t>
+          <t>611151</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1124311</t>
+          <t>1126453</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1179178</t>
+          <t>1180051</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>110388</t>
+          <t>110155</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>150389</t>
+          <t>150560</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>136791</t>
+          <t>135748</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>185115</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>257425</t>
+          <t>257943</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>322528</t>
+          <t>321355</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,03%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>628194</t>
+          <t>628023</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>668195</t>
+          <t>668428</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>639525</t>
+          <t>641052</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>689376</t>
+          <t>690419</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1282222</t>
+          <t>1283395</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1347325</t>
+          <t>1346807</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,93%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>475498</t>
+          <t>473573</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>556729</t>
+          <t>555243</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>583550</t>
+          <t>582971</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>682867</t>
+          <t>676205</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1081724</t>
+          <t>1077061</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1206179</t>
+          <t>1201718</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2837621</t>
+          <t>2839107</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2918852</t>
+          <t>2920777</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2861675</t>
+          <t>2868337</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2960992</t>
+          <t>2961571</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5732713</t>
+          <t>5737174</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5857168</t>
+          <t>5861831</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,48%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipertensión en 2023</t>
+          <t>Población con diagnóstico de hipertensión en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49070</t>
+          <t>49142</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76766</t>
+          <t>76462</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48069</t>
+          <t>48625</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67833</t>
+          <t>68396</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103240</t>
+          <t>103679</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136655</t>
+          <t>136717</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>234677</t>
+          <t>234981</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>262373</t>
+          <t>262301</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>221802</t>
+          <t>221239</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>241566</t>
+          <t>241010</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>464422</t>
+          <t>464360</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>497837</t>
+          <t>497398</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,75%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67374</t>
+          <t>67716</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>105105</t>
+          <t>104338</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68432</t>
+          <t>69904</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95414</t>
+          <t>95289</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>144775</t>
+          <t>144302</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>187690</t>
+          <t>188128</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>412288</t>
+          <t>413055</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>450019</t>
+          <t>449677</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>417163</t>
+          <t>417288</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>444145</t>
+          <t>442673</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>842280</t>
+          <t>841842</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>885195</t>
+          <t>885668</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,99%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52467</t>
+          <t>52045</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76875</t>
+          <t>77329</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65914</t>
+          <t>65968</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90009</t>
+          <t>90793</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>124290</t>
+          <t>123878</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158866</t>
+          <t>159317</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>237610</t>
+          <t>237156</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>262018</t>
+          <t>262440</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>259119</t>
+          <t>258335</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>283214</t>
+          <t>283160</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>504746</t>
+          <t>504295</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>539322</t>
+          <t>539734</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,33%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50797</t>
+          <t>51304</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80204</t>
+          <t>81404</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51046</t>
+          <t>54867</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112563</t>
+          <t>114159</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112621</t>
+          <t>111342</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>178911</t>
+          <t>179900</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>232353</t>
+          <t>231153</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>261760</t>
+          <t>261253</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>363155</t>
+          <t>361559</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>424672</t>
+          <t>420851</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>609363</t>
+          <t>608374</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>675653</t>
+          <t>676932</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,88%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35402</t>
+          <t>35103</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52715</t>
+          <t>53546</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53066</t>
+          <t>52601</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71014</t>
+          <t>70179</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>91314</t>
+          <t>92297</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116443</t>
+          <t>117872</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>126027</t>
+          <t>125196</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143340</t>
+          <t>143639</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136861</t>
+          <t>137696</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>154809</t>
+          <t>155274</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>270174</t>
+          <t>268745</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>295303</t>
+          <t>294320</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,13%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62889</t>
+          <t>61912</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86218</t>
+          <t>85638</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51813</t>
+          <t>52113</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70908</t>
+          <t>70842</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>119184</t>
+          <t>120434</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>149399</t>
+          <t>150683</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>183418</t>
+          <t>183998</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>206747</t>
+          <t>207724</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>185479</t>
+          <t>185545</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>204574</t>
+          <t>204274</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>376624</t>
+          <t>375340</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>406839</t>
+          <t>405589</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,1%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>92472</t>
+          <t>90635</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>131294</t>
+          <t>128155</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>167146</t>
+          <t>168866</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>631305</t>
+          <t>589596</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>274773</t>
+          <t>273900</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>768743</t>
+          <t>853685</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>58,03%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>491295</t>
+          <t>494434</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>530117</t>
+          <t>531954</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>217181</t>
+          <t>258890</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>681340</t>
+          <t>679620</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>702332</t>
+          <t>617390</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1196302</t>
+          <t>1197175</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,38%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52926</t>
+          <t>54933</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>172081</t>
+          <t>169804</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>139648</t>
+          <t>138502</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>177980</t>
+          <t>176795</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>171994</t>
+          <t>167879</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>333823</t>
+          <t>336097</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>756639</t>
+          <t>758916</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>875794</t>
+          <t>873787</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>537412</t>
+          <t>538597</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>575744</t>
+          <t>576890</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1310289</t>
+          <t>1308015</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1472118</t>
+          <t>1476233</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,79%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>491642</t>
+          <t>483909</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>687285</t>
+          <t>689114</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>748005</t>
+          <t>742025</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1482576</t>
+          <t>1477015</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1339617</t>
+          <t>1335900</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2252052</t>
+          <t>2124866</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2768280</t>
+          <t>2766451</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2963923</t>
+          <t>2971656</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2172620</t>
+          <t>2178181</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2907191</t>
+          <t>2913171</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4858709</t>
+          <t>4985895</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5771144</t>
+          <t>5774861</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1403-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1403-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26657</t>
+          <t>26435</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47678</t>
+          <t>48536</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27978</t>
+          <t>27182</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50828</t>
+          <t>50077</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60296</t>
+          <t>59737</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90735</t>
+          <t>89721</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>225332</t>
+          <t>224474</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246353</t>
+          <t>246575</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>210010</t>
+          <t>210761</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>232860</t>
+          <t>233656</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>443113</t>
+          <t>444127</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>473552</t>
+          <t>474111</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,81%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35799</t>
+          <t>34462</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62553</t>
+          <t>61057</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72432</t>
+          <t>73169</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>106454</t>
+          <t>105341</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>113979</t>
+          <t>114309</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>159875</t>
+          <t>158563</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>430522</t>
+          <t>432018</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>457276</t>
+          <t>458613</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>397495</t>
+          <t>398608</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>431517</t>
+          <t>430780</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>837149</t>
+          <t>838461</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>883045</t>
+          <t>882715</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,54%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35430</t>
+          <t>34189</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59389</t>
+          <t>59662</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56561</t>
+          <t>56645</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>85896</t>
+          <t>86116</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>99487</t>
+          <t>98286</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>136479</t>
+          <t>137301</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>259457</t>
+          <t>259184</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>283416</t>
+          <t>284657</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>249516</t>
+          <t>249296</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>278851</t>
+          <t>278767</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>517779</t>
+          <t>516957</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>554771</t>
+          <t>555972</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,98%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40413</t>
+          <t>40554</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65581</t>
+          <t>65743</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54668</t>
+          <t>55325</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84314</t>
+          <t>83985</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>102247</t>
+          <t>102805</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138637</t>
+          <t>140645</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>293090</t>
+          <t>292928</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>318258</t>
+          <t>318117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>287142</t>
+          <t>287471</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>316788</t>
+          <t>316131</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>591490</t>
+          <t>589482</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>627880</t>
+          <t>627322</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,92%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9829</t>
+          <t>9520</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24967</t>
+          <t>24889</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20703</t>
+          <t>21354</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42247</t>
+          <t>42650</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34851</t>
+          <t>33805</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59651</t>
+          <t>59833</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>178341</t>
+          <t>178419</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>193479</t>
+          <t>193788</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>165421</t>
+          <t>165018</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>186965</t>
+          <t>186314</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>351325</t>
+          <t>351143</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>376125</t>
+          <t>377171</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30708</t>
+          <t>30313</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52935</t>
+          <t>54416</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40443</t>
+          <t>40249</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65777</t>
+          <t>67029</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>76928</t>
+          <t>75778</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>111107</t>
+          <t>111330</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>217876</t>
+          <t>216395</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240103</t>
+          <t>240498</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>212367</t>
+          <t>211115</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>237701</t>
+          <t>237895</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>437848</t>
+          <t>437625</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>472027</t>
+          <t>473177</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,2%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>73028</t>
+          <t>73251</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>108448</t>
+          <t>108594</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>92119</t>
+          <t>91297</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>131120</t>
+          <t>130491</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>172214</t>
+          <t>172836</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>222523</t>
+          <t>222144</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>506579</t>
+          <t>506433</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>541999</t>
+          <t>541776</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>507099</t>
+          <t>507728</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>546100</t>
+          <t>546922</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1030723</t>
+          <t>1031102</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1081032</t>
+          <t>1080410</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,21%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>84341</t>
+          <t>84201</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>119043</t>
+          <t>118549</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>90553</t>
+          <t>92762</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>131702</t>
+          <t>133348</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>184604</t>
+          <t>186177</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>241278</t>
+          <t>239583</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>624752</t>
+          <t>625246</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>659454</t>
+          <t>659594</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>651809</t>
+          <t>650163</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>692958</t>
+          <t>690749</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1286028</t>
+          <t>1287723</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1342702</t>
+          <t>1341129</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,81%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>391893</t>
+          <t>390835</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>469366</t>
+          <t>467759</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>533039</t>
+          <t>533685</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>616523</t>
+          <t>618416</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>948521</t>
+          <t>934256</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1059189</t>
+          <t>1053357</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2807177</t>
+          <t>2808784</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2884650</t>
+          <t>2885708</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2762674</t>
+          <t>2760781</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2846158</t>
+          <t>2845512</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5596552</t>
+          <t>5602384</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5707220</t>
+          <t>5721485</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,96%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22588</t>
+          <t>23419</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44811</t>
+          <t>45983</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31507</t>
+          <t>31872</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55814</t>
+          <t>58250</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61148</t>
+          <t>61006</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93285</t>
+          <t>94305</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249927</t>
+          <t>248755</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272150</t>
+          <t>271319</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>231431</t>
+          <t>228995</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>255738</t>
+          <t>255373</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>488698</t>
+          <t>487678</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>520835</t>
+          <t>520977</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,52%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66338</t>
+          <t>64848</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101065</t>
+          <t>101506</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87378</t>
+          <t>86493</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>126648</t>
+          <t>124372</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>161738</t>
+          <t>161638</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>214089</t>
+          <t>213118</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>404462</t>
+          <t>404021</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>439189</t>
+          <t>440679</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>396008</t>
+          <t>398284</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>435278</t>
+          <t>436163</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>814095</t>
+          <t>815066</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>866446</t>
+          <t>866546</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,28%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46355</t>
+          <t>47217</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75307</t>
+          <t>74680</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64247</t>
+          <t>63231</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94171</t>
+          <t>95304</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117988</t>
+          <t>118719</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160694</t>
+          <t>162717</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>248739</t>
+          <t>249366</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>277691</t>
+          <t>276829</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>246849</t>
+          <t>245716</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>276773</t>
+          <t>277789</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>504372</t>
+          <t>502349</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>547078</t>
+          <t>546347</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,15%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53210</t>
+          <t>52722</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85340</t>
+          <t>84270</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>83148</t>
+          <t>81471</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117101</t>
+          <t>116933</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>144938</t>
+          <t>145227</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>192394</t>
+          <t>190988</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>288642</t>
+          <t>289712</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>320772</t>
+          <t>321260</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>271850</t>
+          <t>272018</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>305803</t>
+          <t>307480</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>570539</t>
+          <t>571945</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>617995</t>
+          <t>617706</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>80,96%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21433</t>
+          <t>22663</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44586</t>
+          <t>43635</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45442</t>
+          <t>46290</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72038</t>
+          <t>70917</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72376</t>
+          <t>72081</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>109353</t>
+          <t>107017</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168032</t>
+          <t>168983</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>191185</t>
+          <t>189955</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>147553</t>
+          <t>148674</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>174149</t>
+          <t>173301</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>322856</t>
+          <t>325192</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359833</t>
+          <t>360128</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,32%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48626</t>
+          <t>49570</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78566</t>
+          <t>79291</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51064</t>
+          <t>49466</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79649</t>
+          <t>77798</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>108414</t>
+          <t>105765</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>146964</t>
+          <t>146613</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>195415</t>
+          <t>194690</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>225355</t>
+          <t>224411</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>198447</t>
+          <t>200298</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>227032</t>
+          <t>228630</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>405113</t>
+          <t>405464</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>443663</t>
+          <t>446312</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,84%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>105846</t>
+          <t>105264</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>148665</t>
+          <t>150158</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>139548</t>
+          <t>136585</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>182955</t>
+          <t>183660</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>256998</t>
+          <t>254384</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>317502</t>
+          <t>314729</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>514123</t>
+          <t>512630</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>556942</t>
+          <t>557524</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>510898</t>
+          <t>510193</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>554305</t>
+          <t>557268</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1039139</t>
+          <t>1041912</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1099643</t>
+          <t>1102257</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,25%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>95264</t>
+          <t>92528</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>136923</t>
+          <t>133802</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>115080</t>
+          <t>118646</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>163411</t>
+          <t>162121</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>221537</t>
+          <t>224583</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>285411</t>
+          <t>284784</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>642175</t>
+          <t>645296</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>683834</t>
+          <t>686570</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>659167</t>
+          <t>660457</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>707498</t>
+          <t>703932</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1316265</t>
+          <t>1316892</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1380139</t>
+          <t>1377093</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>85,98%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>529427</t>
+          <t>531292</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>618780</t>
+          <t>625083</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>691577</t>
+          <t>695173</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>792112</t>
+          <t>796731</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1257558</t>
+          <t>1256085</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1382834</t>
+          <t>1389061</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2807999</t>
+          <t>2801696</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2897352</t>
+          <t>2895487</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2761878</t>
+          <t>2757259</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2862413</t>
+          <t>2858817</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5597935</t>
+          <t>5591708</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5723211</t>
+          <t>5724684</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,01%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24266</t>
+          <t>23750</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47098</t>
+          <t>48339</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24114</t>
+          <t>23646</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46288</t>
+          <t>46091</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53182</t>
+          <t>54138</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88001</t>
+          <t>85661</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>246663</t>
+          <t>245422</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269495</t>
+          <t>270011</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>242415</t>
+          <t>242612</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>264589</t>
+          <t>265057</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>494463</t>
+          <t>496803</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>529282</t>
+          <t>528326</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67559</t>
+          <t>67590</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102282</t>
+          <t>101597</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>98818</t>
+          <t>98949</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>139020</t>
+          <t>138689</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>177100</t>
+          <t>178384</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>228991</t>
+          <t>230101</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>400293</t>
+          <t>400978</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>435016</t>
+          <t>434985</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>384064</t>
+          <t>384395</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>424266</t>
+          <t>424135</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>796668</t>
+          <t>795558</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>848559</t>
+          <t>847275</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,61%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35267</t>
+          <t>35558</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59208</t>
+          <t>60712</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38626</t>
+          <t>39437</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66118</t>
+          <t>67121</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80708</t>
+          <t>81476</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117275</t>
+          <t>117177</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>259357</t>
+          <t>257853</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>283298</t>
+          <t>283007</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>270191</t>
+          <t>269188</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>297683</t>
+          <t>296872</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>537599</t>
+          <t>537697</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>574166</t>
+          <t>573398</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,56%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49359</t>
+          <t>48492</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78415</t>
+          <t>78130</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61727</t>
+          <t>61500</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95616</t>
+          <t>95993</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>117765</t>
+          <t>118977</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>162342</t>
+          <t>164398</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>291549</t>
+          <t>291834</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>320605</t>
+          <t>321472</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>291667</t>
+          <t>291290</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>325556</t>
+          <t>325783</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>594905</t>
+          <t>592849</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>639482</t>
+          <t>638270</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,29%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18308</t>
+          <t>17601</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37807</t>
+          <t>38605</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33153</t>
+          <t>32067</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55347</t>
+          <t>57220</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57170</t>
+          <t>55046</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87000</t>
+          <t>85411</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>173414</t>
+          <t>172616</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>192913</t>
+          <t>193620</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>163240</t>
+          <t>161367</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>185434</t>
+          <t>186520</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>342808</t>
+          <t>344397</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>372638</t>
+          <t>374762</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>87,19%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26349</t>
+          <t>26669</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47605</t>
+          <t>47955</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36720</t>
+          <t>35231</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62384</t>
+          <t>61416</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66880</t>
+          <t>67457</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>99741</t>
+          <t>102733</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>215518</t>
+          <t>215168</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236774</t>
+          <t>236454</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>210731</t>
+          <t>211699</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>236395</t>
+          <t>237884</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>436497</t>
+          <t>433505</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>469358</t>
+          <t>468781</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,42%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>76334</t>
+          <t>77416</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>113429</t>
+          <t>113808</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80143</t>
+          <t>78431</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>119836</t>
+          <t>117842</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>167801</t>
+          <t>168514</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>221399</t>
+          <t>221056</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>543129</t>
+          <t>542750</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>580224</t>
+          <t>579142</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>571458</t>
+          <t>573452</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>611151</t>
+          <t>612863</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1126453</t>
+          <t>1126796</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1180051</t>
+          <t>1179338</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,5%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>110155</t>
+          <t>109375</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>150560</t>
+          <t>154294</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>135748</t>
+          <t>134967</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>185115</t>
+          <t>181943</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>257943</t>
+          <t>256896</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>321355</t>
+          <t>321810</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,05%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>628023</t>
+          <t>624289</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>668428</t>
+          <t>669208</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>641052</t>
+          <t>644224</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>690419</t>
+          <t>691200</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1283395</t>
+          <t>1282940</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1346807</t>
+          <t>1347854</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,99%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>473573</t>
+          <t>469734</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>555243</t>
+          <t>553028</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>582971</t>
+          <t>583146</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>676205</t>
+          <t>679166</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1077061</t>
+          <t>1083303</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1201718</t>
+          <t>1215326</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2839107</t>
+          <t>2841322</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2920777</t>
+          <t>2924616</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2868337</t>
+          <t>2865376</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2961571</t>
+          <t>2961396</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5737174</t>
+          <t>5723566</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5861831</t>
+          <t>5855589</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,39%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>61752</t>
+          <t>68949</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49142</t>
+          <t>54364</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76462</t>
+          <t>82657</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>57790</t>
+          <t>59321</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48625</t>
+          <t>48574</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68396</t>
+          <t>69451</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>119542</t>
+          <t>128271</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103679</t>
+          <t>111341</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136717</t>
+          <t>146650</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>23,1%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>249691</t>
+          <t>249896</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>234981</t>
+          <t>236188</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>262301</t>
+          <t>264481</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>231845</t>
+          <t>256740</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>221239</t>
+          <t>246610</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>241010</t>
+          <t>267487</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>481535</t>
+          <t>506635</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>464360</t>
+          <t>488256</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>497398</t>
+          <t>523565</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,46%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>84880</t>
+          <t>87740</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67716</t>
+          <t>71270</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>104338</t>
+          <t>108543</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,27 +11075,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81672</t>
+          <t>86948</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69904</t>
+          <t>73834</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95289</t>
+          <t>101117</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>166552</t>
+          <t>174687</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>144302</t>
+          <t>151127</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>188128</t>
+          <t>197517</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>432513</t>
+          <t>441920</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>413055</t>
+          <t>421117</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>449677</t>
+          <t>458390</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,22 +11188,22 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>430905</t>
+          <t>457078</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>417288</t>
+          <t>442909</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>442673</t>
+          <t>470192</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -11213,7 +11213,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>863418</t>
+          <t>898999</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>841842</t>
+          <t>876169</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>885668</t>
+          <t>922559</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,92%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512577</t>
+          <t>544026</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512577</t>
+          <t>544026</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512577</t>
+          <t>544026</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1029970</t>
+          <t>1073686</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1029970</t>
+          <t>1073686</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1029970</t>
+          <t>1073686</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>63673</t>
+          <t>62993</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52045</t>
+          <t>52292</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77329</t>
+          <t>75138</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>76921</t>
+          <t>78055</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65968</t>
+          <t>65716</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90793</t>
+          <t>89642</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>140593</t>
+          <t>141048</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>123878</t>
+          <t>124935</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159317</t>
+          <t>158225</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,59%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>250812</t>
+          <t>251461</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>237156</t>
+          <t>239316</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>262440</t>
+          <t>262162</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>272207</t>
+          <t>278326</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>258335</t>
+          <t>266739</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>283160</t>
+          <t>290665</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>523019</t>
+          <t>529788</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>504295</t>
+          <t>512611</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>539734</t>
+          <t>545901</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,38%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>314485</t>
+          <t>314454</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>314485</t>
+          <t>314454</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>314485</t>
+          <t>314454</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>663612</t>
+          <t>670836</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>663612</t>
+          <t>670836</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>663612</t>
+          <t>670836</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>64707</t>
+          <t>71812</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51304</t>
+          <t>56851</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81404</t>
+          <t>88807</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>87279</t>
+          <t>94217</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54867</t>
+          <t>81367</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114159</t>
+          <t>107096</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>151986</t>
+          <t>166029</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111342</t>
+          <t>146118</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>179900</t>
+          <t>187162</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>247850</t>
+          <t>301333</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>231153</t>
+          <t>284338</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>261253</t>
+          <t>316294</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>388439</t>
+          <t>327744</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>361559</t>
+          <t>314865</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>420851</t>
+          <t>340594</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>636288</t>
+          <t>629078</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>608374</t>
+          <t>607945</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>676932</t>
+          <t>648989</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>81,62%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>43227</t>
+          <t>46457</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35103</t>
+          <t>37146</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53546</t>
+          <t>56663</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>61219</t>
+          <t>62807</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52601</t>
+          <t>54557</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70179</t>
+          <t>71956</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>104446</t>
+          <t>109264</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92297</t>
+          <t>95509</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>117872</t>
+          <t>121566</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>135515</t>
+          <t>159208</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125196</t>
+          <t>149002</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143639</t>
+          <t>168519</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>146656</t>
+          <t>163616</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>137696</t>
+          <t>154467</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>155274</t>
+          <t>171866</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>282171</t>
+          <t>322823</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>268745</t>
+          <t>310521</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>294320</t>
+          <t>336578</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>77,9%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207875</t>
+          <t>226423</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207875</t>
+          <t>226423</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207875</t>
+          <t>226423</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386617</t>
+          <t>432087</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386617</t>
+          <t>432087</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386617</t>
+          <t>432087</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>73066</t>
+          <t>72071</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61912</t>
+          <t>61052</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>85638</t>
+          <t>84892</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>60470</t>
+          <t>62501</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52113</t>
+          <t>53306</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70842</t>
+          <t>72529</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>133536</t>
+          <t>134572</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>120434</t>
+          <t>120563</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>150683</t>
+          <t>151043</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,3%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>196570</t>
+          <t>198636</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>183998</t>
+          <t>185815</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207724</t>
+          <t>209655</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>195917</t>
+          <t>200598</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>185545</t>
+          <t>190570</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>204274</t>
+          <t>209793</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>392487</t>
+          <t>399234</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>375340</t>
+          <t>382763</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>405589</t>
+          <t>413243</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,41%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>109869</t>
+          <t>131258</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>90635</t>
+          <t>108618</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>128155</t>
+          <t>152491</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>338078</t>
+          <t>164100</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>168866</t>
+          <t>144062</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>589596</t>
+          <t>184191</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>447947</t>
+          <t>295358</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>273900</t>
+          <t>267812</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>853685</t>
+          <t>326238</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>512720</t>
+          <t>585190</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>494434</t>
+          <t>563957</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>531954</t>
+          <t>607830</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>510408</t>
+          <t>606599</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>258890</t>
+          <t>586508</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>679620</t>
+          <t>626637</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1023128</t>
+          <t>1191790</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>617390</t>
+          <t>1160910</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1197175</t>
+          <t>1219336</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,99%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>622589</t>
+          <t>716448</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>622589</t>
+          <t>716448</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>622589</t>
+          <t>716448</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>848486</t>
+          <t>770699</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>848486</t>
+          <t>770699</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>848486</t>
+          <t>770699</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1471075</t>
+          <t>1487148</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1471075</t>
+          <t>1487148</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1471075</t>
+          <t>1487148</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>120080</t>
+          <t>133990</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54933</t>
+          <t>114748</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>169804</t>
+          <t>153800</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>156549</t>
+          <t>173158</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>138502</t>
+          <t>154162</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>176795</t>
+          <t>193791</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>276629</t>
+          <t>307148</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>167879</t>
+          <t>280342</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>336097</t>
+          <t>335855</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>808640</t>
+          <t>664082</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>758916</t>
+          <t>644272</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>873787</t>
+          <t>683324</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>558843</t>
+          <t>657451</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>538597</t>
+          <t>636818</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>576890</t>
+          <t>676447</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1367483</t>
+          <t>1321533</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1308015</t>
+          <t>1292826</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1476233</t>
+          <t>1348339</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>82,79%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>621253</t>
+          <t>675270</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>483909</t>
+          <t>632575</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>689114</t>
+          <t>724668</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>919978</t>
+          <t>781108</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>742025</t>
+          <t>740525</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1477015</t>
+          <t>822721</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1541231</t>
+          <t>1456378</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1335900</t>
+          <t>1398603</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2124866</t>
+          <t>1516704</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2834312</t>
+          <t>2851727</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2766451</t>
+          <t>2802329</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2971656</t>
+          <t>2894422</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2735218</t>
+          <t>2948152</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2178181</t>
+          <t>2906539</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2913171</t>
+          <t>2988735</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5569530</t>
+          <t>5799878</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4985895</t>
+          <t>5739552</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5774861</t>
+          <t>5857653</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>80,73%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3455565</t>
+          <t>3526997</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3455565</t>
+          <t>3526997</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3455565</t>
+          <t>3526997</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3655196</t>
+          <t>3729260</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3655196</t>
+          <t>3729260</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3655196</t>
+          <t>3729260</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7110761</t>
+          <t>7256256</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7110761</t>
+          <t>7256256</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7110761</t>
+          <t>7256256</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
